--- a/outputs/236-22.xlsx
+++ b/outputs/236-22.xlsx
@@ -132,16 +132,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -334,93 +338,93 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="15.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="1" width="15.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="13.43"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <v>9814</v>
       </c>
-      <c r="F2" s="1"/>
-      <c r="P2" s="2"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="F2" s="2"/>
+      <c r="P2" s="3"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D4" s="1" t="n">
         <v>9814</v>
       </c>
-      <c r="F7" s="1"/>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F11" s="1"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P14" s="2"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="2"/>
-      <c r="F18" s="1"/>
-      <c r="P18" s="2"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="2"/>
-      <c r="F22" s="1"/>
+      <c r="F4" s="2"/>
+      <c r="P4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F5" s="2"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P8" s="3"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="3"/>
+      <c r="F12" s="2"/>
+      <c r="P12" s="3"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="3"/>
+      <c r="F16" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/outputs/236-22.xlsx
+++ b/outputs/236-22.xlsx
@@ -90,12 +90,18 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -137,15 +143,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -338,93 +344,116 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="1" width="15.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="13.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="15.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13.43"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="0" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="0" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="1" t="n">
+      <c r="D2" s="0" t="n">
         <v>9814</v>
       </c>
-      <c r="F2" s="2"/>
-      <c r="P2" s="3"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="F2" s="1"/>
+      <c r="P2" s="2"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B7" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C7" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D7" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E7" s="0" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C8" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="1" t="n">
+      <c r="D8" s="0" t="n">
         <v>9814</v>
       </c>
-      <c r="F4" s="2"/>
-      <c r="P4" s="3"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F5" s="2"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P8" s="3"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="3"/>
-      <c r="F12" s="2"/>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="3"/>
-      <c r="F16" s="2"/>
+      <c r="F8" s="1"/>
+      <c r="P8" s="2"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="1"/>
+      <c r="P11" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F14" s="1"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P17" s="2"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="2"/>
+      <c r="F21" s="1"/>
+      <c r="P21" s="2"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="2"/>
+      <c r="F25" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
